--- a/Base frete e despesa frota.xlsx
+++ b/Base frete e despesa frota.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bocchi\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bocchiagrobios.sharepoint.com/sites/Logstica-BocchiAgrobios/Shared Documents/Indicadores/Indicador HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4B6AB6-7AD0-409C-B897-B02C2491DEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{3A4B6AB6-7AD0-409C-B897-B02C2491DEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5DFD7EB-1664-40AC-AD3A-A020D58B3A36}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E22FE06A-EF37-40C8-B540-9C1A9B5734B3}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2673" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2739" uniqueCount="115">
   <si>
     <t>ANO</t>
   </si>
@@ -378,6 +378,15 @@
   </si>
   <si>
     <t>12/2024</t>
+  </si>
+  <si>
+    <t>05/2026</t>
+  </si>
+  <si>
+    <t>CRISTIANO DA SILVA</t>
+  </si>
+  <si>
+    <t>ELMAR GASPARIN</t>
   </si>
 </sst>
 </file>
@@ -827,8 +836,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7682BAD-72C8-4D1E-9551-209ED182A8FA}">
-  <dimension ref="A1:M687"/>
+  <dimension ref="A1:M704"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -28060,6 +28073,683 @@
       <c r="K687" s="6"/>
       <c r="L687" s="6"/>
       <c r="M687" s="6"/>
+    </row>
+    <row r="688" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A688" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B688" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C688" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D688" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E688" s="6">
+        <v>2025</v>
+      </c>
+      <c r="F688" s="7">
+        <v>43501.286699999997</v>
+      </c>
+      <c r="G688" s="6">
+        <v>1757536</v>
+      </c>
+      <c r="H688" s="7">
+        <v>64387.246099999997</v>
+      </c>
+      <c r="I688" s="8">
+        <v>20885.9594</v>
+      </c>
+      <c r="J688" s="6">
+        <v>60000</v>
+      </c>
+      <c r="K688" s="6">
+        <v>850000</v>
+      </c>
+      <c r="L688" s="6">
+        <v>45000</v>
+      </c>
+      <c r="M688" s="6">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="689" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A689" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B689" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C689" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D689" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E689" s="10">
+        <v>2025</v>
+      </c>
+      <c r="F689" s="10">
+        <v>42096.036699999997</v>
+      </c>
+      <c r="G689" s="10">
+        <v>1533780</v>
+      </c>
+      <c r="H689" s="10">
+        <v>57493.6374</v>
+      </c>
+      <c r="I689" s="10">
+        <v>15397.600700000001</v>
+      </c>
+      <c r="J689" s="10">
+        <v>66000</v>
+      </c>
+      <c r="K689" s="10">
+        <v>900000</v>
+      </c>
+      <c r="L689" s="10">
+        <v>45000</v>
+      </c>
+      <c r="M689" s="10">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="690" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A690" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B690" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C690" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D690" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E690" s="6">
+        <v>2019</v>
+      </c>
+      <c r="F690" s="6">
+        <v>31204.240000000002</v>
+      </c>
+      <c r="G690" s="6">
+        <v>1410530</v>
+      </c>
+      <c r="H690" s="6">
+        <v>44676.265800000001</v>
+      </c>
+      <c r="I690" s="6">
+        <v>13472.025799999999</v>
+      </c>
+      <c r="J690" s="6">
+        <v>60000</v>
+      </c>
+      <c r="K690" s="6">
+        <v>900000</v>
+      </c>
+      <c r="L690" s="6">
+        <v>45000</v>
+      </c>
+      <c r="M690" s="6">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="691" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A691" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B691" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C691" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D691" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E691" s="10">
+        <v>2019</v>
+      </c>
+      <c r="F691" s="10">
+        <v>35338.15</v>
+      </c>
+      <c r="G691" s="10">
+        <v>1274290</v>
+      </c>
+      <c r="H691" s="10">
+        <v>38343.46</v>
+      </c>
+      <c r="I691" s="10">
+        <v>3005.31</v>
+      </c>
+      <c r="J691" s="10">
+        <v>47000</v>
+      </c>
+      <c r="K691" s="10">
+        <v>900000</v>
+      </c>
+      <c r="L691" s="10">
+        <v>45000</v>
+      </c>
+      <c r="M691" s="10">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="692" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A692" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B692" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C692" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D692" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E692" s="6">
+        <v>2019</v>
+      </c>
+      <c r="F692" s="6">
+        <v>34057.01</v>
+      </c>
+      <c r="G692" s="6">
+        <v>1652820</v>
+      </c>
+      <c r="H692" s="6">
+        <v>52788.23</v>
+      </c>
+      <c r="I692" s="6">
+        <v>18731.22</v>
+      </c>
+      <c r="J692" s="6">
+        <v>47000</v>
+      </c>
+      <c r="K692" s="6">
+        <v>900000</v>
+      </c>
+      <c r="L692" s="6">
+        <v>45000</v>
+      </c>
+      <c r="M692" s="6">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="693" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A693" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B693" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C693" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D693" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E693" s="10">
+        <v>2025</v>
+      </c>
+      <c r="F693" s="10">
+        <v>44940.576699999998</v>
+      </c>
+      <c r="G693" s="10">
+        <v>1484370</v>
+      </c>
+      <c r="H693" s="10">
+        <v>59792.198199999999</v>
+      </c>
+      <c r="I693" s="10">
+        <v>14851.621499999999</v>
+      </c>
+      <c r="J693" s="10">
+        <v>66000</v>
+      </c>
+      <c r="K693" s="10">
+        <v>900000</v>
+      </c>
+      <c r="L693" s="10">
+        <v>45000</v>
+      </c>
+      <c r="M693" s="10">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="694" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A694" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B694" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C694" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D694" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E694" s="6">
+        <v>2025</v>
+      </c>
+      <c r="F694" s="6">
+        <v>52083.876700000001</v>
+      </c>
+      <c r="G694" s="6">
+        <v>1681520</v>
+      </c>
+      <c r="H694" s="6">
+        <v>65015.606800000001</v>
+      </c>
+      <c r="I694" s="6">
+        <v>12931.730100000001</v>
+      </c>
+      <c r="J694" s="6">
+        <v>66000</v>
+      </c>
+      <c r="K694" s="6">
+        <v>900000</v>
+      </c>
+      <c r="L694" s="6">
+        <v>45000</v>
+      </c>
+      <c r="M694" s="6">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="695" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A695" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B695" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C695" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D695" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E695" s="10">
+        <v>2025</v>
+      </c>
+      <c r="F695" s="10">
+        <v>55128.296699999999</v>
+      </c>
+      <c r="G695" s="10">
+        <v>1915150</v>
+      </c>
+      <c r="H695" s="10">
+        <v>68646.014599999995</v>
+      </c>
+      <c r="I695" s="10">
+        <v>13517.7179</v>
+      </c>
+      <c r="J695" s="10">
+        <v>66000</v>
+      </c>
+      <c r="K695" s="10">
+        <v>900000</v>
+      </c>
+      <c r="L695" s="10">
+        <v>45000</v>
+      </c>
+      <c r="M695" s="10">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="696" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A696" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B696" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C696" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D696" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E696" s="6">
+        <v>2025</v>
+      </c>
+      <c r="F696" s="6">
+        <v>62586.646699999998</v>
+      </c>
+      <c r="G696" s="6">
+        <v>1771160</v>
+      </c>
+      <c r="H696" s="6">
+        <v>72588.375799999994</v>
+      </c>
+      <c r="I696" s="6">
+        <v>10001.7291</v>
+      </c>
+      <c r="J696" s="6">
+        <v>66000</v>
+      </c>
+      <c r="K696" s="6">
+        <v>900000</v>
+      </c>
+      <c r="L696" s="6">
+        <v>45000</v>
+      </c>
+      <c r="M696" s="6">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="697" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A697" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B697" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C697" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D697" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E697" s="10">
+        <v>2025</v>
+      </c>
+      <c r="F697" s="10">
+        <v>47054.396699999998</v>
+      </c>
+      <c r="G697" s="10">
+        <v>1770870</v>
+      </c>
+      <c r="H697" s="10">
+        <v>66774.493799999997</v>
+      </c>
+      <c r="I697" s="10">
+        <v>19720.097099999999</v>
+      </c>
+      <c r="J697" s="10">
+        <v>66000</v>
+      </c>
+      <c r="K697" s="10">
+        <v>900000</v>
+      </c>
+      <c r="L697" s="10">
+        <v>45000</v>
+      </c>
+      <c r="M697" s="10">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="698" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A698" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B698" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C698" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D698" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E698" s="6">
+        <v>2025</v>
+      </c>
+      <c r="F698" s="6">
+        <v>51810.786699999997</v>
+      </c>
+      <c r="G698" s="6">
+        <v>1689910</v>
+      </c>
+      <c r="H698" s="6">
+        <v>66988.937900000004</v>
+      </c>
+      <c r="I698" s="6">
+        <v>15178.1512</v>
+      </c>
+      <c r="J698" s="6">
+        <v>66000</v>
+      </c>
+      <c r="K698" s="6">
+        <v>900000</v>
+      </c>
+      <c r="L698" s="6">
+        <v>45000</v>
+      </c>
+      <c r="M698" s="6">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="699" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A699" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B699" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C699" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D699" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E699" s="10">
+        <v>2025</v>
+      </c>
+      <c r="F699" s="10">
+        <v>51672.4067</v>
+      </c>
+      <c r="G699" s="10">
+        <v>1672380</v>
+      </c>
+      <c r="H699" s="10">
+        <v>62170.585899999998</v>
+      </c>
+      <c r="I699" s="10">
+        <v>10498.1792</v>
+      </c>
+      <c r="J699" s="10">
+        <v>66000</v>
+      </c>
+      <c r="K699" s="10">
+        <v>900000</v>
+      </c>
+      <c r="L699" s="10">
+        <v>45000</v>
+      </c>
+      <c r="M699" s="10">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="700" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A700" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B700" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C700" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D700" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E700" s="6">
+        <v>2025</v>
+      </c>
+      <c r="F700" s="6">
+        <v>51973.326699999998</v>
+      </c>
+      <c r="G700" s="6">
+        <v>1790720</v>
+      </c>
+      <c r="H700" s="6">
+        <v>69484.391799999998</v>
+      </c>
+      <c r="I700" s="6">
+        <v>17511.0651</v>
+      </c>
+      <c r="J700" s="6">
+        <v>66000</v>
+      </c>
+      <c r="K700" s="6">
+        <v>900000</v>
+      </c>
+      <c r="L700" s="6">
+        <v>45000</v>
+      </c>
+      <c r="M700" s="6">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="701" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A701" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B701" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C701" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D701" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E701" s="10">
+        <v>2025</v>
+      </c>
+      <c r="F701" s="10">
+        <v>40422.256699999998</v>
+      </c>
+      <c r="G701" s="10">
+        <v>1409500</v>
+      </c>
+      <c r="H701" s="10">
+        <v>56278.888299999999</v>
+      </c>
+      <c r="I701" s="10">
+        <v>15856.631600000001</v>
+      </c>
+      <c r="J701" s="10">
+        <v>60000</v>
+      </c>
+      <c r="K701" s="10">
+        <v>900000</v>
+      </c>
+      <c r="L701" s="10">
+        <v>45000</v>
+      </c>
+      <c r="M701" s="10">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="702" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A702" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B702" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C702" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D702" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E702" s="6">
+        <v>2025</v>
+      </c>
+      <c r="F702" s="6">
+        <v>42238.756699999998</v>
+      </c>
+      <c r="G702" s="6">
+        <v>1609625</v>
+      </c>
+      <c r="H702" s="6">
+        <v>60695.7094</v>
+      </c>
+      <c r="I702" s="6">
+        <v>18456.952700000002</v>
+      </c>
+      <c r="J702" s="6">
+        <v>60000</v>
+      </c>
+      <c r="K702" s="6">
+        <v>900000</v>
+      </c>
+      <c r="L702" s="6">
+        <v>45000</v>
+      </c>
+      <c r="M702" s="6">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="703" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A703" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B703" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C703" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D703" s="10"/>
+      <c r="E703" s="10">
+        <v>0</v>
+      </c>
+      <c r="F703" s="10">
+        <v>34.35</v>
+      </c>
+      <c r="G703" s="10">
+        <v>0</v>
+      </c>
+      <c r="H703" s="10">
+        <v>0</v>
+      </c>
+      <c r="I703" s="10">
+        <v>-34.35</v>
+      </c>
+      <c r="J703" s="10"/>
+      <c r="K703" s="10"/>
+      <c r="L703" s="10"/>
+      <c r="M703" s="10"/>
+    </row>
+    <row r="704" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A704" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B704" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C704" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D704" s="6"/>
+      <c r="E704" s="6">
+        <v>0</v>
+      </c>
+      <c r="F704" s="6">
+        <v>10760.9</v>
+      </c>
+      <c r="G704" s="6">
+        <v>0</v>
+      </c>
+      <c r="H704" s="6">
+        <v>0</v>
+      </c>
+      <c r="I704" s="6">
+        <v>-10760.9</v>
+      </c>
+      <c r="J704" s="6"/>
+      <c r="K704" s="6"/>
+      <c r="L704" s="6"/>
+      <c r="M704" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M687" xr:uid="{A7682BAD-72C8-4D1E-9551-209ED182A8FA}"/>
@@ -28068,8 +28758,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CCF91708236A7D49B0BD72CE987A4435" ma:contentTypeVersion="11" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="5dd71aeed9c99b1318c8c95cf9be42df">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0ed7d9fe-8743-4a97-b7d3-266663a62318" xmlns:ns3="26286142-6906-44b9-a187-26a3417709ec" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="532744c67031ab5e00799a7638f7d5fe" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CCF91708236A7D49B0BD72CE987A4435" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="726c7fd414ff24d12cf8b8d8d879be58">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0ed7d9fe-8743-4a97-b7d3-266663a62318" xmlns:ns3="26286142-6906-44b9-a187-26a3417709ec" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="239dc31eab2fc9727250b1c1d43d5a65" ns2:_="" ns3:_="">
     <xsd:import namespace="0ed7d9fe-8743-4a97-b7d3-266663a62318"/>
     <xsd:import namespace="26286142-6906-44b9-a187-26a3417709ec"/>
     <xsd:element name="properties">
@@ -28133,7 +28832,7 @@
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="b61eceb1-7c92-4c18-ac1f-48f182618d12" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="b61eceb1-7c92-4c18-ac1f-48f182618d12" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -28172,8 +28871,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -28262,15 +28961,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -28283,13 +28973,24 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96772AD1-76DC-4ECD-AE13-A6E4AB73A3CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0F869A0-3C42-459C-BB6B-5974A6E012F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0F869A0-3C42-459C-BB6B-5974A6E012F4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{804D1583-37B1-46A1-8859-8F97DE587426}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DF09E17-5A4D-4B11-80FE-322DDB74B76A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DF09E17-5A4D-4B11-80FE-322DDB74B76A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0ed7d9fe-8743-4a97-b7d3-266663a62318"/>
+    <ds:schemaRef ds:uri="26286142-6906-44b9-a187-26a3417709ec"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>